--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2016/MICHIGAN_2016.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2016/MICHIGAN_2016.xlsx
@@ -4038,7 +4038,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C205">
@@ -8167,7 +8167,7 @@
         <v>56</v>
       </c>
       <c r="D434">
-        <v>0.009557945041816009</v>
+        <v>0.009557945041816007</v>
       </c>
     </row>
     <row r="435">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>General Trevino</t>
+          <t>Gral. Trevino</t>
         </is>
       </c>
       <c r="C515">
@@ -9636,7 +9636,7 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>General Zaragoza</t>
+          <t>Gral. Zaragoza</t>
         </is>
       </c>
       <c r="C516">
@@ -10590,7 +10590,7 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec -Distrito 08-</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C569">
@@ -10716,7 +10716,7 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C576">
